--- a/artfynd/A 26654-2024 artfynd.xlsx
+++ b/artfynd/A 26654-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111630840</v>
+        <v>111630837</v>
       </c>
       <c r="B2" t="n">
-        <v>78512</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566584</v>
+        <v>566536</v>
       </c>
       <c r="R2" t="n">
-        <v>7031235</v>
+        <v>7031400</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111630838</v>
+        <v>111630843</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566534</v>
+        <v>566563</v>
       </c>
       <c r="R3" t="n">
-        <v>7031195</v>
+        <v>7031085</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111630843</v>
+        <v>111630835</v>
       </c>
       <c r="B4" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566563</v>
+        <v>566519</v>
       </c>
       <c r="R4" t="n">
-        <v>7031085</v>
+        <v>7031426</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111630844</v>
+        <v>111630834</v>
       </c>
       <c r="B5" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92037</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>3277</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566544</v>
+        <v>566714</v>
       </c>
       <c r="R5" t="n">
-        <v>7031076</v>
+        <v>7031207</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111630835</v>
+        <v>111630844</v>
       </c>
       <c r="B6" t="n">
-        <v>89745</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566519</v>
+        <v>566544</v>
       </c>
       <c r="R6" t="n">
-        <v>7031426</v>
+        <v>7031076</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111630841</v>
+        <v>111630840</v>
       </c>
       <c r="B7" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566617</v>
+        <v>566584</v>
       </c>
       <c r="R7" t="n">
-        <v>7031107</v>
+        <v>7031235</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,53 +1257,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111630837</v>
+        <v>111630842</v>
       </c>
       <c r="B8" t="n">
-        <v>89401</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Linflon, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566536</v>
+        <v>566617</v>
       </c>
       <c r="R8" t="n">
-        <v>7031400</v>
+        <v>7031107</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1371,6 +1339,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1386,6 +1355,200 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>111630841</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Linflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>566617</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7031107</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>111630838</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Linflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>566534</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7031195</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26654-2024 artfynd.xlsx
+++ b/artfynd/A 26654-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630837</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630843</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630835</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630834</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630844</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630840</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630842</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630841</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,8 +1594,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111630838</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>